--- a/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Revenue/Revenue_Reliability_Analysis.xlsx
+++ b/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Revenue/Revenue_Reliability_Analysis.xlsx
@@ -507,10 +507,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.867</v>
+        <v>0.878</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -530,14 +530,14 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.902</v>
+        <v>0.899</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.752</v>
+        <v>0.776</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.403</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.826</v>
+        <v>0.874</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.651</v>
+        <v>0.65</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
